--- a/表格/工作日志.xlsx
+++ b/表格/工作日志.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25965" windowHeight="12570" activeTab="6"/>
+    <workbookView windowWidth="26985" windowHeight="12570" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="玩法设计" sheetId="8" r:id="rId1"/>
@@ -515,10 +515,11 @@
     <t>高血量、移动慢；死亡时分裂成3只兔子；三只兔子拥有各自的能力</t>
   </si>
   <si>
-    <t>巨型沙蛇</t>
-  </si>
-  <si>
-    <t>引发沙尘暴</t>
+    <t>沙蛇Boss</t>
+  </si>
+  <si>
+    <t>引发沙尘暴，沙尘暴有持续时间，撞击墙壁会反弹
+被沙尘暴击中会扣血、并且失去一定的视线范围</t>
   </si>
   <si>
     <t>幽灵</t>
@@ -527,7 +528,7 @@
     <t>为周围的同伴恢复生命</t>
   </si>
   <si>
-    <t>沙漠毛象</t>
+    <t>沙漠长毛象</t>
   </si>
   <si>
     <t>预瞄位置 横冲直撞 撞击造成2伤害</t>
@@ -536,7 +537,8 @@
     <t>沙虫王Boss</t>
   </si>
   <si>
-    <t>统治沙漠的巨大沙虫，一节一节的，打掉的身体躯干会变成小沙虫；尾巴和头部血量中等，身体血量高；尾巴会周期性产出小沙虫；头部可发射子弹；免疫位移</t>
+    <t>统治沙漠的巨大沙虫，一节一节的，打掉的身体躯干会变成小沙虫；
+尾巴和头部血量中等，身体血量高；尾巴会周期性产出小沙虫；头部可发射子弹；免疫位移</t>
   </si>
   <si>
     <t>沙傀儡</t>
@@ -1272,12 +1274,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1285,6 +1281,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1646,57 +1648,57 @@
     <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1707,7 +1709,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1753,37 +1755,40 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2109,13 +2114,13 @@
   <dimension ref="B3:D10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="27" style="26" customWidth="1"/>
+    <col min="2" max="2" width="27" style="27" customWidth="1"/>
     <col min="3" max="3" width="92.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="114.125" style="27" customWidth="1"/>
+    <col min="4" max="4" width="114.125" style="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" ht="140" customHeight="1" spans="2:3">
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="27" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="7" t="s">
@@ -2123,7 +2128,7 @@
       </c>
     </row>
     <row r="4" ht="101" customHeight="1" spans="2:3">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="27" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="7" t="s">
@@ -2131,7 +2136,7 @@
       </c>
     </row>
     <row r="5" ht="101" customHeight="1" spans="2:3">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="27" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="7" t="s">
@@ -2139,7 +2144,7 @@
       </c>
     </row>
     <row r="6" ht="103" customHeight="1" spans="2:3">
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="7" t="s">
@@ -2147,7 +2152,7 @@
       </c>
     </row>
     <row r="7" ht="103" customHeight="1" spans="2:3">
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="27" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="7" t="s">
@@ -2155,7 +2160,7 @@
       </c>
     </row>
     <row r="8" ht="100" customHeight="1" spans="2:3">
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="27" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="7" t="s">
@@ -2163,16 +2168,16 @@
       </c>
     </row>
     <row r="9" ht="154" customHeight="1" spans="2:4">
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="27" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="28"/>
+      <c r="D9" s="29"/>
     </row>
     <row r="10" ht="76" customHeight="1" spans="2:3">
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="27" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -2251,16 +2256,16 @@
       <c r="D6" s="12"/>
     </row>
     <row r="7" ht="14.25" spans="1:4">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="25" t="s">
         <v>24</v>
       </c>
     </row>
@@ -3200,16 +3205,16 @@
       <c r="D7" s="12"/>
     </row>
     <row r="8" ht="14.25" spans="1:4">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="25" t="s">
         <v>24</v>
       </c>
     </row>
@@ -4153,19 +4158,19 @@
       <c r="E68" s="23"/>
     </row>
     <row r="69" ht="14.25" spans="1:7">
-      <c r="A69" s="15" t="s">
+      <c r="A69" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="B69" s="15" t="s">
+      <c r="B69" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C69" s="15" t="s">
+      <c r="C69" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="D69" s="15" t="s">
+      <c r="D69" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="E69" s="25" t="s">
+      <c r="E69" s="26" t="s">
         <v>38</v>
       </c>
       <c r="F69" t="s">
@@ -4191,7 +4196,7 @@
         <f>FLOOR($B$65*POWER(A70,$B$66)*B70,1)</f>
         <v>3</v>
       </c>
-      <c r="E70" s="25"/>
+      <c r="E70" s="26"/>
       <c r="F70">
         <f>1+B70*((A70-1)*$B$63/100)</f>
         <v>1</v>
@@ -4217,7 +4222,7 @@
         <f t="shared" ref="D70:D104" si="7">FLOOR($B$65*POWER(A71,$B$66)*B71,1)</f>
         <v>18</v>
       </c>
-      <c r="E71" s="25"/>
+      <c r="E71" s="26"/>
       <c r="F71">
         <f t="shared" ref="F71:F102" si="8">1+B71*((A71-1)*$B$63/100)</f>
         <v>1.039601</v>
@@ -4243,7 +4248,7 @@
         <f t="shared" si="7"/>
         <v>44</v>
       </c>
-      <c r="E72" s="25"/>
+      <c r="E72" s="26"/>
       <c r="F72">
         <f t="shared" si="8"/>
         <v>1.07880599</v>
@@ -4269,7 +4274,7 @@
         <f t="shared" si="7"/>
         <v>82</v>
       </c>
-      <c r="E73" s="25"/>
+      <c r="E73" s="26"/>
       <c r="F73">
         <f t="shared" si="8"/>
         <v>1.117617940075</v>
@@ -4295,7 +4300,7 @@
         <f t="shared" si="7"/>
         <v>134</v>
       </c>
-      <c r="E74" s="25"/>
+      <c r="E74" s="26"/>
       <c r="F74">
         <f t="shared" si="8"/>
         <v>1.1560398004995</v>
@@ -4321,7 +4326,7 @@
         <f t="shared" si="7"/>
         <v>199</v>
       </c>
-      <c r="E75" s="25"/>
+      <c r="E75" s="26"/>
       <c r="F75">
         <f t="shared" si="8"/>
         <v>1.19407450187125</v>
@@ -4347,7 +4352,7 @@
         <f t="shared" si="7"/>
         <v>279</v>
       </c>
-      <c r="E76" s="25"/>
+      <c r="E76" s="26"/>
       <c r="F76">
         <f t="shared" si="8"/>
         <v>1.23172495523428</v>
@@ -4373,7 +4378,7 @@
         <f t="shared" si="7"/>
         <v>372</v>
       </c>
-      <c r="E77" s="25"/>
+      <c r="E77" s="26"/>
       <c r="F77">
         <f t="shared" si="8"/>
         <v>1.26899405220112</v>
@@ -4399,7 +4404,7 @@
         <f t="shared" si="7"/>
         <v>480</v>
       </c>
-      <c r="E78" s="25"/>
+      <c r="E78" s="26"/>
       <c r="F78">
         <f t="shared" si="8"/>
         <v>1.30588466507442</v>
@@ -4425,7 +4430,7 @@
         <f t="shared" si="7"/>
         <v>602</v>
       </c>
-      <c r="E79" s="25"/>
+      <c r="E79" s="26"/>
       <c r="F79">
         <f t="shared" si="8"/>
         <v>1.34239964696768</v>
@@ -4451,7 +4456,7 @@
         <f t="shared" si="7"/>
         <v>739</v>
       </c>
-      <c r="E80" s="25"/>
+      <c r="E80" s="26"/>
       <c r="F80">
         <f t="shared" si="8"/>
         <v>1.37854183192538</v>
@@ -4477,7 +4482,7 @@
         <f t="shared" si="7"/>
         <v>891</v>
       </c>
-      <c r="E81" s="25"/>
+      <c r="E81" s="26"/>
       <c r="F81">
         <f t="shared" si="8"/>
         <v>1.41431403504233</v>
@@ -4503,7 +4508,7 @@
         <f t="shared" si="7"/>
         <v>1057</v>
       </c>
-      <c r="E82" s="25"/>
+      <c r="E82" s="26"/>
       <c r="F82">
         <f t="shared" si="8"/>
         <v>1.44971905258231</v>
@@ -4529,7 +4534,7 @@
         <f t="shared" si="7"/>
         <v>1238</v>
       </c>
-      <c r="E83" s="25"/>
+      <c r="E83" s="26"/>
       <c r="F83">
         <f t="shared" si="8"/>
         <v>1.48475966209601</v>
@@ -4555,7 +4560,7 @@
         <f t="shared" si="7"/>
         <v>1434</v>
       </c>
-      <c r="E84" s="25"/>
+      <c r="E84" s="26"/>
       <c r="F84">
         <f t="shared" si="8"/>
         <v>1.51943862253826</v>
@@ -4581,7 +4586,7 @@
         <f t="shared" si="7"/>
         <v>1645</v>
       </c>
-      <c r="E85" s="25"/>
+      <c r="E85" s="26"/>
       <c r="F85">
         <f t="shared" si="8"/>
         <v>1.55375867438454</v>
@@ -4607,7 +4612,7 @@
         <f t="shared" si="7"/>
         <v>1870</v>
       </c>
-      <c r="E86" s="25"/>
+      <c r="E86" s="26"/>
       <c r="F86">
         <f t="shared" si="8"/>
         <v>1.58772253974679</v>
@@ -4633,7 +4638,7 @@
         <f t="shared" si="7"/>
         <v>2110</v>
       </c>
-      <c r="E87" s="25"/>
+      <c r="E87" s="26"/>
       <c r="F87">
         <f t="shared" si="8"/>
         <v>1.62133292248856</v>
@@ -4659,7 +4664,7 @@
         <f t="shared" si="7"/>
         <v>2365</v>
       </c>
-      <c r="E88" s="25"/>
+      <c r="E88" s="26"/>
       <c r="F88">
         <f t="shared" si="8"/>
         <v>1.65459250833942</v>
@@ -4685,7 +4690,7 @@
         <f t="shared" si="7"/>
         <v>2635</v>
       </c>
-      <c r="E89" s="25"/>
+      <c r="E89" s="26"/>
       <c r="F89">
         <f t="shared" si="8"/>
         <v>1.68750396500871</v>
@@ -4711,7 +4716,7 @@
         <f t="shared" si="7"/>
         <v>2918</v>
       </c>
-      <c r="E90" s="25"/>
+      <c r="E90" s="26"/>
       <c r="F90">
         <f t="shared" si="8"/>
         <v>1.7200699422986</v>
@@ -4737,7 +4742,7 @@
         <f t="shared" si="7"/>
         <v>3217</v>
       </c>
-      <c r="E91" s="25"/>
+      <c r="E91" s="26"/>
       <c r="F91">
         <f t="shared" si="8"/>
         <v>1.75229307221646</v>
@@ -4763,7 +4768,7 @@
         <f t="shared" si="7"/>
         <v>3530</v>
       </c>
-      <c r="E92" s="25"/>
+      <c r="E92" s="26"/>
       <c r="F92">
         <f t="shared" si="8"/>
         <v>1.78417596908658</v>
@@ -4789,7 +4794,7 @@
         <f t="shared" si="7"/>
         <v>3857</v>
       </c>
-      <c r="E93" s="25"/>
+      <c r="E93" s="26"/>
       <c r="F93">
         <f t="shared" si="8"/>
         <v>1.8157212296612</v>
@@ -4815,7 +4820,7 @@
         <f t="shared" si="7"/>
         <v>4198</v>
       </c>
-      <c r="E94" s="25"/>
+      <c r="E94" s="26"/>
       <c r="F94">
         <f t="shared" si="8"/>
         <v>1.84693143323085</v>
@@ -4841,7 +4846,7 @@
         <f t="shared" si="7"/>
         <v>4554</v>
       </c>
-      <c r="E95" s="25"/>
+      <c r="E95" s="26"/>
       <c r="F95">
         <f t="shared" si="8"/>
         <v>1.87780914173406</v>
@@ -4867,7 +4872,7 @@
         <f t="shared" si="7"/>
         <v>4923</v>
       </c>
-      <c r="E96" s="25"/>
+      <c r="E96" s="26"/>
       <c r="F96">
         <f t="shared" si="8"/>
         <v>1.9083568998664</v>
@@ -4893,7 +4898,7 @@
         <f t="shared" si="7"/>
         <v>5307</v>
       </c>
-      <c r="E97" s="25"/>
+      <c r="E97" s="26"/>
       <c r="F97">
         <f t="shared" si="8"/>
         <v>1.93857723518888</v>
@@ -4919,7 +4924,7 @@
         <f t="shared" si="7"/>
         <v>5704</v>
       </c>
-      <c r="E98" s="25"/>
+      <c r="E98" s="26"/>
       <c r="F98">
         <f t="shared" si="8"/>
         <v>1.96847265823564</v>
@@ -4945,7 +4950,7 @@
         <f t="shared" si="7"/>
         <v>6115</v>
       </c>
-      <c r="E99" s="25"/>
+      <c r="E99" s="26"/>
       <c r="F99">
         <f t="shared" si="8"/>
         <v>1.99804566262105</v>
@@ -4971,7 +4976,7 @@
         <f t="shared" si="7"/>
         <v>6539</v>
       </c>
-      <c r="E100" s="25"/>
+      <c r="E100" s="26"/>
       <c r="F100">
         <f t="shared" si="8"/>
         <v>2.02729872514615</v>
@@ -4997,7 +5002,7 @@
         <f t="shared" si="7"/>
         <v>6977</v>
       </c>
-      <c r="E101" s="25"/>
+      <c r="E101" s="26"/>
       <c r="F101">
         <f t="shared" si="8"/>
         <v>2.05623430590443</v>
@@ -5023,7 +5028,7 @@
         <f t="shared" si="7"/>
         <v>7429</v>
       </c>
-      <c r="E102" s="25"/>
+      <c r="E102" s="26"/>
       <c r="F102">
         <f t="shared" si="8"/>
         <v>2.084854848387</v>
@@ -5049,7 +5054,7 @@
         <f t="shared" si="7"/>
         <v>7894</v>
       </c>
-      <c r="E103" s="25"/>
+      <c r="E103" s="26"/>
       <c r="F103">
         <f t="shared" ref="F103:F119" si="11">1+B103*((A103-1)*$B$63/100)</f>
         <v>2.1131627795871</v>
@@ -5075,7 +5080,7 @@
         <f t="shared" si="7"/>
         <v>8371</v>
       </c>
-      <c r="E104" s="25"/>
+      <c r="E104" s="26"/>
       <c r="F104">
         <f t="shared" si="11"/>
         <v>2.14116051010399</v>
@@ -5101,7 +5106,7 @@
         <f t="shared" ref="D105:D119" si="14">FLOOR($B$65*POWER(A105,$B$66)*B105,1)</f>
         <v>8862</v>
       </c>
-      <c r="E105" s="25"/>
+      <c r="E105" s="26"/>
       <c r="F105">
         <f t="shared" si="11"/>
         <v>2.16885043424622</v>
@@ -5127,7 +5132,7 @@
         <f t="shared" si="14"/>
         <v>9366</v>
       </c>
-      <c r="E106" s="25"/>
+      <c r="E106" s="26"/>
       <c r="F106">
         <f t="shared" si="11"/>
         <v>2.19623493013427</v>
@@ -5153,7 +5158,7 @@
         <f t="shared" si="14"/>
         <v>9882</v>
       </c>
-      <c r="E107" s="25"/>
+      <c r="E107" s="26"/>
       <c r="F107">
         <f t="shared" si="11"/>
         <v>2.22331635980259</v>
@@ -5179,7 +5184,7 @@
         <f t="shared" si="14"/>
         <v>10411</v>
       </c>
-      <c r="E108" s="25"/>
+      <c r="E108" s="26"/>
       <c r="F108">
         <f t="shared" si="11"/>
         <v>2.25009706930097</v>
@@ -5205,7 +5210,7 @@
         <f t="shared" si="14"/>
         <v>10952</v>
       </c>
-      <c r="E109" s="25"/>
+      <c r="E109" s="26"/>
       <c r="F109">
         <f t="shared" si="11"/>
         <v>2.27657938879537</v>
@@ -5231,7 +5236,7 @@
         <f t="shared" si="14"/>
         <v>11506</v>
       </c>
-      <c r="E110" s="25"/>
+      <c r="E110" s="26"/>
       <c r="F110">
         <f t="shared" si="11"/>
         <v>2.3027656326681</v>
@@ -5257,7 +5262,7 @@
         <f t="shared" si="14"/>
         <v>12071</v>
       </c>
-      <c r="E111" s="25"/>
+      <c r="E111" s="26"/>
       <c r="F111">
         <f t="shared" si="11"/>
         <v>2.32865809961738</v>
@@ -5283,7 +5288,7 @@
         <f t="shared" si="14"/>
         <v>12649</v>
       </c>
-      <c r="E112" s="25"/>
+      <c r="E112" s="26"/>
       <c r="F112">
         <f t="shared" si="11"/>
         <v>2.35425907275634</v>
@@ -5309,7 +5314,7 @@
         <f t="shared" si="14"/>
         <v>13239</v>
       </c>
-      <c r="E113" s="25"/>
+      <c r="E113" s="26"/>
       <c r="F113">
         <f t="shared" si="11"/>
         <v>2.37957081971143</v>
@@ -5335,7 +5340,7 @@
         <f t="shared" si="14"/>
         <v>13840</v>
       </c>
-      <c r="E114" s="25"/>
+      <c r="E114" s="26"/>
       <c r="F114">
         <f t="shared" si="11"/>
         <v>2.40459559272015</v>
@@ -5361,7 +5366,7 @@
         <f t="shared" si="14"/>
         <v>14454</v>
       </c>
-      <c r="E115" s="25"/>
+      <c r="E115" s="26"/>
       <c r="F115">
         <f t="shared" si="11"/>
         <v>2.42933562872829</v>
@@ -5387,7 +5392,7 @@
         <f t="shared" si="14"/>
         <v>15078</v>
       </c>
-      <c r="E116" s="25"/>
+      <c r="E116" s="26"/>
       <c r="F116">
         <f t="shared" si="11"/>
         <v>2.45379314948653</v>
@@ -5413,7 +5418,7 @@
         <f t="shared" si="14"/>
         <v>15714</v>
       </c>
-      <c r="E117" s="25"/>
+      <c r="E117" s="26"/>
       <c r="F117">
         <f t="shared" si="11"/>
         <v>2.47797036164647</v>
@@ -5439,7 +5444,7 @@
         <f t="shared" si="14"/>
         <v>16361</v>
       </c>
-      <c r="E118" s="25"/>
+      <c r="E118" s="26"/>
       <c r="F118">
         <f t="shared" si="11"/>
         <v>2.50186945685607</v>
@@ -5465,7 +5470,7 @@
         <f t="shared" si="14"/>
         <v>17019</v>
       </c>
-      <c r="E119" s="25"/>
+      <c r="E119" s="26"/>
       <c r="F119">
         <f t="shared" si="11"/>
         <v>2.52549261185454</v>
@@ -6688,7 +6693,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="31" spans="3:5">
+    <row r="31" ht="28.5" spans="3:5">
       <c r="C31" s="12">
         <v>204</v>
       </c>
@@ -6710,22 +6715,22 @@
         <v>111</v>
       </c>
     </row>
-    <row r="33" spans="3:5">
-      <c r="C33" s="1">
+    <row r="33" ht="15" customHeight="1" spans="3:5">
+      <c r="C33" s="14">
         <v>206</v>
       </c>
       <c r="D33" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="14" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="34" spans="3:5">
-      <c r="C34" s="15">
+    <row r="34" ht="45" customHeight="1" spans="3:5">
+      <c r="C34" s="14">
         <v>207</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="14" t="s">
         <v>114</v>
       </c>
       <c r="E34" s="15" t="s">

--- a/表格/工作日志.xlsx
+++ b/表格/工作日志.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26985" windowHeight="12570" activeTab="6"/>
+    <workbookView windowWidth="26985" windowHeight="12570" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="玩法设计" sheetId="8" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="241">
   <si>
     <t>核心玩法：</t>
   </si>
@@ -814,10 +814,18 @@
     <t>词条：碰撞受到伤害时将直接击杀当前目标</t>
   </si>
   <si>
-    <t>狼王召唤特效、音效</t>
-  </si>
-  <si>
     <t>词条：在行动路线上留下荆棘？对碰撞的敌人造成伤害</t>
+  </si>
+  <si>
+    <t>沙尘Buff Icon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+火箭:发射的箭矢在地上留下火焰路径,路径对处于上方的敌人造成灼烧伤害
+冰箭:箭发射的箭矢在地上留下冰霜路径,路径对处于上方的敌人造成减速效果
+驯服：周期性驯服场上的随机怪物，被驯服的怪物失去攻击能力，对碰撞到的其他怪物造成伤害
+蓄力一击： 向前方散射8枚箭矢，箭矢拥有超高的伤害
+</t>
   </si>
   <si>
     <t>资源优化</t>
@@ -1262,13 +1270,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1709,7 +1717,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1728,6 +1736,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1749,15 +1760,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1779,7 +1790,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2114,70 +2125,70 @@
   <dimension ref="B3:D10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="27" style="27" customWidth="1"/>
+    <col min="2" max="2" width="27" style="28" customWidth="1"/>
     <col min="3" max="3" width="92.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="114.125" style="28" customWidth="1"/>
+    <col min="4" max="4" width="114.125" style="29" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" ht="140" customHeight="1" spans="2:3">
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" ht="101" customHeight="1" spans="2:3">
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" ht="101" customHeight="1" spans="2:3">
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" ht="103" customHeight="1" spans="2:3">
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" ht="103" customHeight="1" spans="2:3">
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" ht="100" customHeight="1" spans="2:3">
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" ht="154" customHeight="1" spans="2:4">
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="29"/>
+      <c r="D9" s="30"/>
     </row>
     <row r="10" ht="76" customHeight="1" spans="2:3">
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -2202,7 +2213,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28.5" spans="1:4">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="1"/>
@@ -2210,11 +2221,11 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" ht="14.25" spans="1:4">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
       <c r="D2" s="1"/>
     </row>
     <row r="3" ht="14.25" spans="1:4">
@@ -2236,36 +2247,36 @@
       <c r="D4" s="1"/>
     </row>
     <row r="5" ht="14.25" spans="1:4">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="16">
         <v>1.8</v>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
     </row>
     <row r="6" ht="14.25" spans="1:4">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
     </row>
     <row r="7" ht="14.25" spans="1:4">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="26" t="s">
         <v>24</v>
       </c>
     </row>
@@ -3141,7 +3152,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28.5" spans="1:4">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>25</v>
       </c>
       <c r="B1" s="1"/>
@@ -3149,11 +3160,11 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" ht="14.25" spans="1:4">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
       <c r="D2" s="1"/>
     </row>
     <row r="3" ht="14.25" spans="1:4">
@@ -3185,36 +3196,36 @@
       <c r="D5" s="1"/>
     </row>
     <row r="6" ht="14.25" spans="1:4">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="16">
         <v>2</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-    </row>
-    <row r="7" s="23" customFormat="1" ht="14.25" spans="1:4">
-      <c r="A7" s="12" t="s">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+    </row>
+    <row r="7" s="24" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A7" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="16">
         <v>3</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
     </row>
     <row r="8" ht="14.25" spans="1:4">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="26" t="s">
         <v>24</v>
       </c>
     </row>
@@ -4069,19 +4080,19 @@
       </c>
     </row>
     <row r="59" ht="28.5" spans="1:4">
-      <c r="A59" s="24"/>
+      <c r="A59" s="25"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
     </row>
     <row r="60" ht="28.5" spans="1:4">
-      <c r="A60" s="24"/>
+      <c r="A60" s="25"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
     </row>
     <row r="61" ht="28.5" spans="1:4">
-      <c r="A61" s="24" t="s">
+      <c r="A61" s="25" t="s">
         <v>30</v>
       </c>
       <c r="B61" s="1"/>
@@ -4113,8 +4124,8 @@
         <v>33</v>
       </c>
       <c r="B64" s="1"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="12"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="16"/>
     </row>
     <row r="65" ht="14.25" spans="1:4">
       <c r="A65" s="1" t="s">
@@ -4123,54 +4134,54 @@
       <c r="B65" s="1">
         <v>1</v>
       </c>
-      <c r="C65" s="12"/>
-      <c r="D65" s="12"/>
+      <c r="C65" s="16"/>
+      <c r="D65" s="16"/>
     </row>
     <row r="66" ht="14.25" spans="1:4">
-      <c r="A66" s="12" t="s">
+      <c r="A66" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B66" s="12">
+      <c r="B66" s="16">
         <v>2.2</v>
       </c>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="16"/>
     </row>
     <row r="67" ht="14.25" spans="1:4">
-      <c r="A67" s="12" t="s">
+      <c r="A67" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B67" s="12">
+      <c r="B67" s="16">
         <v>4</v>
       </c>
-      <c r="C67" s="12"/>
-      <c r="D67" s="12"/>
+      <c r="C67" s="16"/>
+      <c r="D67" s="16"/>
     </row>
     <row r="68" ht="14.25" spans="1:5">
-      <c r="A68" s="12" t="s">
+      <c r="A68" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B68" s="12">
+      <c r="B68" s="16">
         <v>0.995</v>
       </c>
-      <c r="C68" s="12"/>
-      <c r="D68" s="12"/>
-      <c r="E68" s="23"/>
+      <c r="C68" s="16"/>
+      <c r="D68" s="16"/>
+      <c r="E68" s="24"/>
     </row>
     <row r="69" ht="14.25" spans="1:7">
-      <c r="A69" s="25" t="s">
+      <c r="A69" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B69" s="25" t="s">
+      <c r="B69" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="C69" s="25" t="s">
+      <c r="C69" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="D69" s="25" t="s">
+      <c r="D69" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="E69" s="26" t="s">
+      <c r="E69" s="27" t="s">
         <v>38</v>
       </c>
       <c r="F69" t="s">
@@ -4196,7 +4207,7 @@
         <f>FLOOR($B$65*POWER(A70,$B$66)*B70,1)</f>
         <v>3</v>
       </c>
-      <c r="E70" s="26"/>
+      <c r="E70" s="27"/>
       <c r="F70">
         <f>1+B70*((A70-1)*$B$63/100)</f>
         <v>1</v>
@@ -4222,7 +4233,7 @@
         <f t="shared" ref="D70:D104" si="7">FLOOR($B$65*POWER(A71,$B$66)*B71,1)</f>
         <v>18</v>
       </c>
-      <c r="E71" s="26"/>
+      <c r="E71" s="27"/>
       <c r="F71">
         <f t="shared" ref="F71:F102" si="8">1+B71*((A71-1)*$B$63/100)</f>
         <v>1.039601</v>
@@ -4248,7 +4259,7 @@
         <f t="shared" si="7"/>
         <v>44</v>
       </c>
-      <c r="E72" s="26"/>
+      <c r="E72" s="27"/>
       <c r="F72">
         <f t="shared" si="8"/>
         <v>1.07880599</v>
@@ -4274,7 +4285,7 @@
         <f t="shared" si="7"/>
         <v>82</v>
       </c>
-      <c r="E73" s="26"/>
+      <c r="E73" s="27"/>
       <c r="F73">
         <f t="shared" si="8"/>
         <v>1.117617940075</v>
@@ -4300,7 +4311,7 @@
         <f t="shared" si="7"/>
         <v>134</v>
       </c>
-      <c r="E74" s="26"/>
+      <c r="E74" s="27"/>
       <c r="F74">
         <f t="shared" si="8"/>
         <v>1.1560398004995</v>
@@ -4326,7 +4337,7 @@
         <f t="shared" si="7"/>
         <v>199</v>
       </c>
-      <c r="E75" s="26"/>
+      <c r="E75" s="27"/>
       <c r="F75">
         <f t="shared" si="8"/>
         <v>1.19407450187125</v>
@@ -4352,7 +4363,7 @@
         <f t="shared" si="7"/>
         <v>279</v>
       </c>
-      <c r="E76" s="26"/>
+      <c r="E76" s="27"/>
       <c r="F76">
         <f t="shared" si="8"/>
         <v>1.23172495523428</v>
@@ -4378,7 +4389,7 @@
         <f t="shared" si="7"/>
         <v>372</v>
       </c>
-      <c r="E77" s="26"/>
+      <c r="E77" s="27"/>
       <c r="F77">
         <f t="shared" si="8"/>
         <v>1.26899405220112</v>
@@ -4404,7 +4415,7 @@
         <f t="shared" si="7"/>
         <v>480</v>
       </c>
-      <c r="E78" s="26"/>
+      <c r="E78" s="27"/>
       <c r="F78">
         <f t="shared" si="8"/>
         <v>1.30588466507442</v>
@@ -4430,7 +4441,7 @@
         <f t="shared" si="7"/>
         <v>602</v>
       </c>
-      <c r="E79" s="26"/>
+      <c r="E79" s="27"/>
       <c r="F79">
         <f t="shared" si="8"/>
         <v>1.34239964696768</v>
@@ -4456,7 +4467,7 @@
         <f t="shared" si="7"/>
         <v>739</v>
       </c>
-      <c r="E80" s="26"/>
+      <c r="E80" s="27"/>
       <c r="F80">
         <f t="shared" si="8"/>
         <v>1.37854183192538</v>
@@ -4482,7 +4493,7 @@
         <f t="shared" si="7"/>
         <v>891</v>
       </c>
-      <c r="E81" s="26"/>
+      <c r="E81" s="27"/>
       <c r="F81">
         <f t="shared" si="8"/>
         <v>1.41431403504233</v>
@@ -4508,7 +4519,7 @@
         <f t="shared" si="7"/>
         <v>1057</v>
       </c>
-      <c r="E82" s="26"/>
+      <c r="E82" s="27"/>
       <c r="F82">
         <f t="shared" si="8"/>
         <v>1.44971905258231</v>
@@ -4534,7 +4545,7 @@
         <f t="shared" si="7"/>
         <v>1238</v>
       </c>
-      <c r="E83" s="26"/>
+      <c r="E83" s="27"/>
       <c r="F83">
         <f t="shared" si="8"/>
         <v>1.48475966209601</v>
@@ -4560,7 +4571,7 @@
         <f t="shared" si="7"/>
         <v>1434</v>
       </c>
-      <c r="E84" s="26"/>
+      <c r="E84" s="27"/>
       <c r="F84">
         <f t="shared" si="8"/>
         <v>1.51943862253826</v>
@@ -4586,7 +4597,7 @@
         <f t="shared" si="7"/>
         <v>1645</v>
       </c>
-      <c r="E85" s="26"/>
+      <c r="E85" s="27"/>
       <c r="F85">
         <f t="shared" si="8"/>
         <v>1.55375867438454</v>
@@ -4612,7 +4623,7 @@
         <f t="shared" si="7"/>
         <v>1870</v>
       </c>
-      <c r="E86" s="26"/>
+      <c r="E86" s="27"/>
       <c r="F86">
         <f t="shared" si="8"/>
         <v>1.58772253974679</v>
@@ -4638,7 +4649,7 @@
         <f t="shared" si="7"/>
         <v>2110</v>
       </c>
-      <c r="E87" s="26"/>
+      <c r="E87" s="27"/>
       <c r="F87">
         <f t="shared" si="8"/>
         <v>1.62133292248856</v>
@@ -4664,7 +4675,7 @@
         <f t="shared" si="7"/>
         <v>2365</v>
       </c>
-      <c r="E88" s="26"/>
+      <c r="E88" s="27"/>
       <c r="F88">
         <f t="shared" si="8"/>
         <v>1.65459250833942</v>
@@ -4690,7 +4701,7 @@
         <f t="shared" si="7"/>
         <v>2635</v>
       </c>
-      <c r="E89" s="26"/>
+      <c r="E89" s="27"/>
       <c r="F89">
         <f t="shared" si="8"/>
         <v>1.68750396500871</v>
@@ -4716,7 +4727,7 @@
         <f t="shared" si="7"/>
         <v>2918</v>
       </c>
-      <c r="E90" s="26"/>
+      <c r="E90" s="27"/>
       <c r="F90">
         <f t="shared" si="8"/>
         <v>1.7200699422986</v>
@@ -4742,7 +4753,7 @@
         <f t="shared" si="7"/>
         <v>3217</v>
       </c>
-      <c r="E91" s="26"/>
+      <c r="E91" s="27"/>
       <c r="F91">
         <f t="shared" si="8"/>
         <v>1.75229307221646</v>
@@ -4768,7 +4779,7 @@
         <f t="shared" si="7"/>
         <v>3530</v>
       </c>
-      <c r="E92" s="26"/>
+      <c r="E92" s="27"/>
       <c r="F92">
         <f t="shared" si="8"/>
         <v>1.78417596908658</v>
@@ -4794,7 +4805,7 @@
         <f t="shared" si="7"/>
         <v>3857</v>
       </c>
-      <c r="E93" s="26"/>
+      <c r="E93" s="27"/>
       <c r="F93">
         <f t="shared" si="8"/>
         <v>1.8157212296612</v>
@@ -4820,7 +4831,7 @@
         <f t="shared" si="7"/>
         <v>4198</v>
       </c>
-      <c r="E94" s="26"/>
+      <c r="E94" s="27"/>
       <c r="F94">
         <f t="shared" si="8"/>
         <v>1.84693143323085</v>
@@ -4846,7 +4857,7 @@
         <f t="shared" si="7"/>
         <v>4554</v>
       </c>
-      <c r="E95" s="26"/>
+      <c r="E95" s="27"/>
       <c r="F95">
         <f t="shared" si="8"/>
         <v>1.87780914173406</v>
@@ -4872,7 +4883,7 @@
         <f t="shared" si="7"/>
         <v>4923</v>
       </c>
-      <c r="E96" s="26"/>
+      <c r="E96" s="27"/>
       <c r="F96">
         <f t="shared" si="8"/>
         <v>1.9083568998664</v>
@@ -4898,7 +4909,7 @@
         <f t="shared" si="7"/>
         <v>5307</v>
       </c>
-      <c r="E97" s="26"/>
+      <c r="E97" s="27"/>
       <c r="F97">
         <f t="shared" si="8"/>
         <v>1.93857723518888</v>
@@ -4924,7 +4935,7 @@
         <f t="shared" si="7"/>
         <v>5704</v>
       </c>
-      <c r="E98" s="26"/>
+      <c r="E98" s="27"/>
       <c r="F98">
         <f t="shared" si="8"/>
         <v>1.96847265823564</v>
@@ -4950,7 +4961,7 @@
         <f t="shared" si="7"/>
         <v>6115</v>
       </c>
-      <c r="E99" s="26"/>
+      <c r="E99" s="27"/>
       <c r="F99">
         <f t="shared" si="8"/>
         <v>1.99804566262105</v>
@@ -4976,7 +4987,7 @@
         <f t="shared" si="7"/>
         <v>6539</v>
       </c>
-      <c r="E100" s="26"/>
+      <c r="E100" s="27"/>
       <c r="F100">
         <f t="shared" si="8"/>
         <v>2.02729872514615</v>
@@ -5002,7 +5013,7 @@
         <f t="shared" si="7"/>
         <v>6977</v>
       </c>
-      <c r="E101" s="26"/>
+      <c r="E101" s="27"/>
       <c r="F101">
         <f t="shared" si="8"/>
         <v>2.05623430590443</v>
@@ -5028,7 +5039,7 @@
         <f t="shared" si="7"/>
         <v>7429</v>
       </c>
-      <c r="E102" s="26"/>
+      <c r="E102" s="27"/>
       <c r="F102">
         <f t="shared" si="8"/>
         <v>2.084854848387</v>
@@ -5054,7 +5065,7 @@
         <f t="shared" si="7"/>
         <v>7894</v>
       </c>
-      <c r="E103" s="26"/>
+      <c r="E103" s="27"/>
       <c r="F103">
         <f t="shared" ref="F103:F119" si="11">1+B103*((A103-1)*$B$63/100)</f>
         <v>2.1131627795871</v>
@@ -5080,7 +5091,7 @@
         <f t="shared" si="7"/>
         <v>8371</v>
       </c>
-      <c r="E104" s="26"/>
+      <c r="E104" s="27"/>
       <c r="F104">
         <f t="shared" si="11"/>
         <v>2.14116051010399</v>
@@ -5106,7 +5117,7 @@
         <f t="shared" ref="D105:D119" si="14">FLOOR($B$65*POWER(A105,$B$66)*B105,1)</f>
         <v>8862</v>
       </c>
-      <c r="E105" s="26"/>
+      <c r="E105" s="27"/>
       <c r="F105">
         <f t="shared" si="11"/>
         <v>2.16885043424622</v>
@@ -5132,7 +5143,7 @@
         <f t="shared" si="14"/>
         <v>9366</v>
       </c>
-      <c r="E106" s="26"/>
+      <c r="E106" s="27"/>
       <c r="F106">
         <f t="shared" si="11"/>
         <v>2.19623493013427</v>
@@ -5158,7 +5169,7 @@
         <f t="shared" si="14"/>
         <v>9882</v>
       </c>
-      <c r="E107" s="26"/>
+      <c r="E107" s="27"/>
       <c r="F107">
         <f t="shared" si="11"/>
         <v>2.22331635980259</v>
@@ -5184,7 +5195,7 @@
         <f t="shared" si="14"/>
         <v>10411</v>
       </c>
-      <c r="E108" s="26"/>
+      <c r="E108" s="27"/>
       <c r="F108">
         <f t="shared" si="11"/>
         <v>2.25009706930097</v>
@@ -5210,7 +5221,7 @@
         <f t="shared" si="14"/>
         <v>10952</v>
       </c>
-      <c r="E109" s="26"/>
+      <c r="E109" s="27"/>
       <c r="F109">
         <f t="shared" si="11"/>
         <v>2.27657938879537</v>
@@ -5236,7 +5247,7 @@
         <f t="shared" si="14"/>
         <v>11506</v>
       </c>
-      <c r="E110" s="26"/>
+      <c r="E110" s="27"/>
       <c r="F110">
         <f t="shared" si="11"/>
         <v>2.3027656326681</v>
@@ -5262,7 +5273,7 @@
         <f t="shared" si="14"/>
         <v>12071</v>
       </c>
-      <c r="E111" s="26"/>
+      <c r="E111" s="27"/>
       <c r="F111">
         <f t="shared" si="11"/>
         <v>2.32865809961738</v>
@@ -5288,7 +5299,7 @@
         <f t="shared" si="14"/>
         <v>12649</v>
       </c>
-      <c r="E112" s="26"/>
+      <c r="E112" s="27"/>
       <c r="F112">
         <f t="shared" si="11"/>
         <v>2.35425907275634</v>
@@ -5314,7 +5325,7 @@
         <f t="shared" si="14"/>
         <v>13239</v>
       </c>
-      <c r="E113" s="26"/>
+      <c r="E113" s="27"/>
       <c r="F113">
         <f t="shared" si="11"/>
         <v>2.37957081971143</v>
@@ -5340,7 +5351,7 @@
         <f t="shared" si="14"/>
         <v>13840</v>
       </c>
-      <c r="E114" s="26"/>
+      <c r="E114" s="27"/>
       <c r="F114">
         <f t="shared" si="11"/>
         <v>2.40459559272015</v>
@@ -5366,7 +5377,7 @@
         <f t="shared" si="14"/>
         <v>14454</v>
       </c>
-      <c r="E115" s="26"/>
+      <c r="E115" s="27"/>
       <c r="F115">
         <f t="shared" si="11"/>
         <v>2.42933562872829</v>
@@ -5392,7 +5403,7 @@
         <f t="shared" si="14"/>
         <v>15078</v>
       </c>
-      <c r="E116" s="26"/>
+      <c r="E116" s="27"/>
       <c r="F116">
         <f t="shared" si="11"/>
         <v>2.45379314948653</v>
@@ -5418,7 +5429,7 @@
         <f t="shared" si="14"/>
         <v>15714</v>
       </c>
-      <c r="E117" s="26"/>
+      <c r="E117" s="27"/>
       <c r="F117">
         <f t="shared" si="11"/>
         <v>2.47797036164647</v>
@@ -5444,7 +5455,7 @@
         <f t="shared" si="14"/>
         <v>16361</v>
       </c>
-      <c r="E118" s="26"/>
+      <c r="E118" s="27"/>
       <c r="F118">
         <f t="shared" si="11"/>
         <v>2.50186945685607</v>
@@ -5470,7 +5481,7 @@
         <f t="shared" si="14"/>
         <v>17019</v>
       </c>
-      <c r="E119" s="26"/>
+      <c r="E119" s="27"/>
       <c r="F119">
         <f t="shared" si="11"/>
         <v>2.52549261185454</v>
@@ -5493,7 +5504,7 @@
       <c r="D121" s="1"/>
     </row>
     <row r="122" ht="28.5" spans="1:4">
-      <c r="A122" s="24" t="s">
+      <c r="A122" s="25" t="s">
         <v>41</v>
       </c>
       <c r="C122" s="1"/>
@@ -5928,10 +5939,10 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="23" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6107,10 +6118,10 @@
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="14">
+      <c r="A25" s="13">
         <v>20</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="13">
         <f t="shared" si="1"/>
         <v>960</v>
       </c>
@@ -6312,20 +6323,20 @@
   </cols>
   <sheetData>
     <row r="12" ht="219" customHeight="1" spans="1:1">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="7"/>
+      <c r="A16" s="8"/>
     </row>
     <row r="17" ht="299.25" spans="1:1">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="8" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="7"/>
+      <c r="A21" s="8"/>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
@@ -6333,10 +6344,10 @@
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="7"/>
+      <c r="A24" s="8"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="7"/>
+      <c r="A26" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6360,46 +6371,46 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="17" customFormat="1" ht="27" spans="1:7">
-      <c r="A1" s="18" t="s">
+    <row r="1" s="18" customFormat="1" ht="27" spans="1:7">
+      <c r="A1" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="18" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="2" ht="273" customHeight="1" spans="1:7">
-      <c r="A2" s="19">
+      <c r="A2" s="20">
         <v>10000</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="8" t="s">
         <v>61</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -6407,52 +6418,52 @@
       </c>
     </row>
     <row r="3" ht="102" customHeight="1" spans="1:7">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19" t="s">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="19"/>
+      <c r="E3" s="20"/>
       <c r="G3" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="4" ht="119" customHeight="1" spans="1:5">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19" t="s">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="E4" s="19"/>
+      <c r="E4" s="20"/>
     </row>
     <row r="5" ht="118" customHeight="1" spans="1:5">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19" t="s">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="19"/>
+      <c r="E5" s="20"/>
     </row>
     <row r="6" ht="28.5" spans="2:3">
       <c r="B6" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>74</v>
       </c>
     </row>
@@ -6478,11 +6489,11 @@
   </cols>
   <sheetData>
     <row r="6" ht="236" customHeight="1" spans="2:4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
     </row>
     <row r="7" spans="5:5">
       <c r="E7" s="1" t="s">
@@ -6490,10 +6501,10 @@
       </c>
     </row>
     <row r="9" ht="16.5" spans="2:5">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="10">
         <v>100</v>
       </c>
       <c r="D9" s="5" t="s">
@@ -6504,8 +6515,8 @@
       </c>
     </row>
     <row r="10" ht="16.5" spans="2:5">
-      <c r="B10" s="8"/>
-      <c r="C10" s="9">
+      <c r="B10" s="9"/>
+      <c r="C10" s="10">
         <v>101</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -6516,8 +6527,8 @@
       </c>
     </row>
     <row r="11" ht="16.5" spans="2:5">
-      <c r="B11" s="8"/>
-      <c r="C11" s="9">
+      <c r="B11" s="9"/>
+      <c r="C11" s="10">
         <v>102</v>
       </c>
       <c r="D11" s="5" t="s">
@@ -6567,13 +6578,13 @@
       <c r="D15" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="11" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="2:5">
-      <c r="B16" s="8"/>
-      <c r="C16" s="9">
+      <c r="B16" s="9"/>
+      <c r="C16" s="10">
         <v>107</v>
       </c>
       <c r="D16" s="5" t="s">
@@ -6584,8 +6595,8 @@
       </c>
     </row>
     <row r="17" ht="16.5" spans="2:5">
-      <c r="B17" s="8"/>
-      <c r="C17" s="9">
+      <c r="B17" s="9"/>
+      <c r="C17" s="10">
         <v>108</v>
       </c>
       <c r="D17" s="5" t="s">
@@ -6596,8 +6607,8 @@
       </c>
     </row>
     <row r="18" ht="16.5" spans="2:5">
-      <c r="B18" s="8"/>
-      <c r="C18" s="9">
+      <c r="B18" s="9"/>
+      <c r="C18" s="10">
         <v>109</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -6608,16 +6619,16 @@
       </c>
     </row>
     <row r="19" ht="16.5" spans="2:3">
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
     </row>
     <row r="20" ht="16.5" spans="2:3">
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
     </row>
     <row r="21" ht="16.5" spans="2:5">
-      <c r="B21" s="8"/>
-      <c r="C21" s="9">
+      <c r="B21" s="9"/>
+      <c r="C21" s="10">
         <v>150</v>
       </c>
       <c r="D21" s="5" t="s">
@@ -6628,30 +6639,30 @@
       </c>
     </row>
     <row r="22" ht="16.5" spans="2:3">
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
     </row>
     <row r="23" ht="16.5" spans="2:3">
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
     </row>
     <row r="24" ht="16.5" spans="2:3">
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
     </row>
     <row r="25" ht="16.5" spans="2:3">
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
     </row>
     <row r="26" ht="16.5" spans="2:3">
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
     </row>
     <row r="27" ht="49.5" spans="2:5">
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="10">
         <v>200</v>
       </c>
       <c r="D27" s="5" t="s">
@@ -6660,8 +6671,8 @@
       <c r="E27" s="5"/>
     </row>
     <row r="28" ht="16.5" spans="2:5">
-      <c r="B28" s="8"/>
-      <c r="C28" s="9">
+      <c r="B28" s="9"/>
+      <c r="C28" s="10">
         <v>201</v>
       </c>
       <c r="D28" s="5" t="s">
@@ -6678,7 +6689,7 @@
       <c r="D29" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="11" t="s">
         <v>105</v>
       </c>
     </row>
@@ -6694,13 +6705,13 @@
       </c>
     </row>
     <row r="31" ht="28.5" spans="3:5">
-      <c r="C31" s="12">
+      <c r="C31" s="13">
         <v>204</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="E31" s="14" t="s">
         <v>109</v>
       </c>
     </row>
@@ -6716,21 +6727,21 @@
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" spans="3:5">
-      <c r="C33" s="14">
+      <c r="C33" s="13">
         <v>206</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="13" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="34" ht="45" customHeight="1" spans="3:5">
-      <c r="C34" s="14">
+      <c r="C34" s="13">
         <v>207</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="13" t="s">
         <v>114</v>
       </c>
       <c r="E34" s="15" t="s">
@@ -6738,10 +6749,10 @@
       </c>
     </row>
     <row r="35" spans="3:5">
-      <c r="C35" s="1">
+      <c r="C35" s="13">
         <v>208</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="13" t="s">
         <v>116</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -6749,10 +6760,10 @@
       </c>
     </row>
     <row r="36" spans="3:5">
-      <c r="C36" s="1">
+      <c r="C36" s="13">
         <v>209</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="13" t="s">
         <v>118</v>
       </c>
       <c r="E36" s="1" t="s">
@@ -6760,107 +6771,107 @@
       </c>
     </row>
     <row r="37" ht="16.5" spans="2:5">
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="E37" s="7"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="E37" s="8"/>
     </row>
     <row r="38" ht="16.5" spans="2:5">
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="E38" s="7"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="E38" s="8"/>
     </row>
     <row r="39" ht="16.5" spans="2:5">
-      <c r="B39" s="8"/>
-      <c r="C39" s="9">
+      <c r="B39" s="9"/>
+      <c r="C39" s="10">
         <v>250</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="E39" s="10" t="s">
+      <c r="E39" s="11" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="2:5">
-      <c r="B40" s="8"/>
-      <c r="C40" s="9">
+      <c r="B40" s="9"/>
+      <c r="C40" s="10">
         <v>251</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E40" s="10" t="s">
+      <c r="E40" s="11" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="2:5">
-      <c r="B41" s="8"/>
-      <c r="C41" s="9">
+      <c r="B41" s="9"/>
+      <c r="C41" s="10">
         <v>252</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="11" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="2:5">
-      <c r="B42" s="8"/>
-      <c r="C42" s="9">
+      <c r="B42" s="9"/>
+      <c r="C42" s="10">
         <v>255</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="E42" s="10"/>
+      <c r="E42" s="11"/>
     </row>
     <row r="43" ht="16.5" spans="2:5">
-      <c r="B43" s="8"/>
-      <c r="C43" s="9">
+      <c r="B43" s="9"/>
+      <c r="C43" s="10">
         <v>256</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="E43" s="10"/>
+      <c r="E43" s="11"/>
     </row>
     <row r="44" ht="16.5" spans="2:5">
-      <c r="B44" s="8"/>
-      <c r="C44" s="9">
+      <c r="B44" s="9"/>
+      <c r="C44" s="10">
         <v>257</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="E44" s="10"/>
+      <c r="E44" s="11"/>
     </row>
     <row r="45" ht="16.5" spans="2:5">
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="E45" s="7"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="E45" s="8"/>
     </row>
     <row r="46" ht="16.5" spans="2:5">
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="E46" s="7"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="E46" s="8"/>
     </row>
     <row r="47" ht="16.5" spans="2:5">
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="E47" s="7"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="E47" s="8"/>
     </row>
     <row r="48" ht="49.5" spans="2:5">
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="C48" s="8">
+      <c r="C48" s="9">
         <v>300</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="E48" s="8" t="s">
         <v>130</v>
       </c>
     </row>
@@ -6871,7 +6882,7 @@
       <c r="D49" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E49" s="7" t="s">
+      <c r="E49" s="8" t="s">
         <v>132</v>
       </c>
     </row>
@@ -6882,7 +6893,7 @@
       <c r="D50" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E50" s="7" t="s">
+      <c r="E50" s="8" t="s">
         <v>134</v>
       </c>
     </row>
@@ -6964,16 +6975,16 @@
       </c>
     </row>
     <row r="59" ht="49.5" spans="2:5">
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="C59" s="8">
+      <c r="C59" s="9">
         <v>400</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E59" s="7" t="s">
+      <c r="E59" s="8" t="s">
         <v>151</v>
       </c>
     </row>
@@ -6992,8 +7003,8 @@
       <c r="C61" s="1">
         <v>402</v>
       </c>
-      <c r="D61" s="12"/>
-      <c r="E61" s="13"/>
+      <c r="D61" s="16"/>
+      <c r="E61" s="14"/>
     </row>
     <row r="62" spans="3:5">
       <c r="C62" s="1">
@@ -7002,7 +7013,7 @@
       <c r="D62" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="E62" s="10" t="s">
+      <c r="E62" s="11" t="s">
         <v>155</v>
       </c>
     </row>
@@ -7013,7 +7024,7 @@
       <c r="D63" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="E63" s="10" t="s">
+      <c r="E63" s="11" t="s">
         <v>157</v>
       </c>
     </row>
@@ -7024,7 +7035,7 @@
       <c r="D64" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E64" s="7" t="s">
+      <c r="E64" s="8" t="s">
         <v>159</v>
       </c>
     </row>
@@ -7035,65 +7046,65 @@
       <c r="D65" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E65" s="7" t="s">
+      <c r="E65" s="8" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="66" ht="16.5" spans="2:5">
-      <c r="B66" s="8"/>
+      <c r="B66" s="9"/>
       <c r="C66" s="1">
         <v>407</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E66" s="7" t="s">
+      <c r="E66" s="8" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="67" ht="16.5" spans="2:5">
-      <c r="B67" s="8"/>
+      <c r="B67" s="9"/>
       <c r="C67" s="1">
         <v>408</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E67" s="7" t="s">
+      <c r="E67" s="8" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="2:5">
-      <c r="B68" s="8"/>
+      <c r="B68" s="9"/>
       <c r="C68" s="1">
         <v>409</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E68" s="7" t="s">
+      <c r="E68" s="8" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="69" ht="16.5" spans="2:5">
-      <c r="B69" s="8"/>
-      <c r="C69" s="8"/>
-      <c r="E69" s="7"/>
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
+      <c r="E69" s="8"/>
     </row>
     <row r="70" ht="16.5" spans="2:5">
-      <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
-      <c r="E70" s="7"/>
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
+      <c r="E70" s="8"/>
     </row>
     <row r="71" ht="28.5" spans="2:5">
-      <c r="B71" s="8" t="s">
+      <c r="B71" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="C71" s="8"/>
+      <c r="C71" s="9"/>
       <c r="D71" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E71" s="7" t="s">
+      <c r="E71" s="8" t="s">
         <v>170</v>
       </c>
     </row>
@@ -7119,70 +7130,70 @@
       </c>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="16" t="s">
+      <c r="A77" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="B77" s="16" t="s">
+      <c r="B77" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="C77" s="16"/>
-      <c r="D77" s="16" t="s">
+      <c r="C77" s="17"/>
+      <c r="D77" s="17" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="16" t="s">
+      <c r="A78" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="B78" s="16" t="s">
+      <c r="B78" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="16" t="s">
+      <c r="C78" s="17"/>
+      <c r="D78" s="17" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="16" t="s">
+      <c r="A79" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="B79" s="16" t="s">
+      <c r="B79" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="C79" s="16"/>
-      <c r="D79" s="16" t="s">
+      <c r="C79" s="17"/>
+      <c r="D79" s="17" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="80" spans="4:4">
-      <c r="D80" s="7"/>
+      <c r="D80" s="8"/>
     </row>
     <row r="81" spans="4:4">
-      <c r="D81" s="7"/>
+      <c r="D81" s="8"/>
     </row>
     <row r="82" spans="4:4">
-      <c r="D82" s="7"/>
+      <c r="D82" s="8"/>
     </row>
     <row r="83" spans="4:4">
-      <c r="D83" s="7"/>
+      <c r="D83" s="8"/>
     </row>
     <row r="84" spans="4:4">
-      <c r="D84" s="7"/>
+      <c r="D84" s="8"/>
     </row>
     <row r="85" spans="4:4">
-      <c r="D85" s="7"/>
+      <c r="D85" s="8"/>
     </row>
     <row r="86" spans="4:4">
-      <c r="D86" s="7"/>
+      <c r="D86" s="8"/>
     </row>
     <row r="87" spans="4:4">
-      <c r="D87" s="7"/>
+      <c r="D87" s="8"/>
     </row>
     <row r="88" ht="28.5" spans="2:4">
       <c r="B88" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="D88" s="7" t="s">
+      <c r="D88" s="8" t="s">
         <v>183</v>
       </c>
     </row>
@@ -7228,7 +7239,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A10:A28"/>
+  <dimension ref="A10:A29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="74.5" style="1" customWidth="1"/>
@@ -7303,6 +7314,11 @@
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
         <v>204</v>
+      </c>
+    </row>
+    <row r="29" ht="142.5" spans="1:1">
+      <c r="A29" s="6" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -7337,79 +7353,79 @@
     <row r="11" ht="58" customHeight="1"/>
     <row r="12" ht="297" spans="1:2">
       <c r="A12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" ht="27" spans="1:2">
       <c r="A13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2">
       <c r="A14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" ht="40.5" spans="1:2">
       <c r="A15" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B17" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" ht="60" customHeight="1" spans="1:2">
       <c r="A18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" ht="81" spans="1:2">
       <c r="A19" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" ht="148" customHeight="1" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" ht="135" spans="1:2">
       <c r="A21" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="2:2">
@@ -7417,10 +7433,10 @@
     </row>
     <row r="23" ht="67.5" spans="1:2">
       <c r="A23" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" spans="2:2">
@@ -7434,30 +7450,30 @@
     </row>
     <row r="27" ht="148.5" spans="1:3">
       <c r="A27" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B28" s="3"/>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B29" s="3"/>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B30" s="3"/>
     </row>
@@ -7472,36 +7488,36 @@
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="38" ht="121.5" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="40" ht="94.5" spans="1:2">
       <c r="A40" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B45" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/表格/工作日志.xlsx
+++ b/表格/工作日志.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26985" windowHeight="12570" activeTab="7"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="玩法设计" sheetId="8" r:id="rId1"/>
@@ -1717,7 +1717,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1742,9 +1742,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1760,14 +1757,14 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
@@ -2125,70 +2122,70 @@
   <dimension ref="B3:D10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="27" style="28" customWidth="1"/>
+    <col min="2" max="2" width="27" style="27" customWidth="1"/>
     <col min="3" max="3" width="92.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="114.125" style="29" customWidth="1"/>
+    <col min="4" max="4" width="114.125" style="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" ht="140" customHeight="1" spans="2:3">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" ht="101" customHeight="1" spans="2:3">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" ht="101" customHeight="1" spans="2:3">
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" ht="103" customHeight="1" spans="2:3">
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" ht="103" customHeight="1" spans="2:3">
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" ht="100" customHeight="1" spans="2:3">
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" ht="154" customHeight="1" spans="2:4">
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="30"/>
+      <c r="D9" s="29"/>
     </row>
     <row r="10" ht="76" customHeight="1" spans="2:3">
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="27" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -2213,7 +2210,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28.5" spans="1:4">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="1"/>
@@ -2221,11 +2218,11 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" ht="14.25" spans="1:4">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
       <c r="D2" s="1"/>
     </row>
     <row r="3" ht="14.25" spans="1:4">
@@ -2247,36 +2244,36 @@
       <c r="D4" s="1"/>
     </row>
     <row r="5" ht="14.25" spans="1:4">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="14">
         <v>1.8</v>
       </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
     </row>
     <row r="6" ht="14.25" spans="1:4">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
     </row>
     <row r="7" ht="14.25" spans="1:4">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="25" t="s">
         <v>24</v>
       </c>
     </row>
@@ -3152,7 +3149,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28.5" spans="1:4">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>25</v>
       </c>
       <c r="B1" s="1"/>
@@ -3160,11 +3157,11 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" ht="14.25" spans="1:4">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
       <c r="D2" s="1"/>
     </row>
     <row r="3" ht="14.25" spans="1:4">
@@ -3196,36 +3193,36 @@
       <c r="D5" s="1"/>
     </row>
     <row r="6" ht="14.25" spans="1:4">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="14">
         <v>2</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-    </row>
-    <row r="7" s="24" customFormat="1" ht="14.25" spans="1:4">
-      <c r="A7" s="16" t="s">
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+    </row>
+    <row r="7" s="23" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A7" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="14">
         <v>3</v>
       </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
     </row>
     <row r="8" ht="14.25" spans="1:4">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="25" t="s">
         <v>24</v>
       </c>
     </row>
@@ -4080,19 +4077,19 @@
       </c>
     </row>
     <row r="59" ht="28.5" spans="1:4">
-      <c r="A59" s="25"/>
+      <c r="A59" s="24"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
     </row>
     <row r="60" ht="28.5" spans="1:4">
-      <c r="A60" s="25"/>
+      <c r="A60" s="24"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
     </row>
     <row r="61" ht="28.5" spans="1:4">
-      <c r="A61" s="25" t="s">
+      <c r="A61" s="24" t="s">
         <v>30</v>
       </c>
       <c r="B61" s="1"/>
@@ -4124,8 +4121,8 @@
         <v>33</v>
       </c>
       <c r="B64" s="1"/>
-      <c r="C64" s="16"/>
-      <c r="D64" s="16"/>
+      <c r="C64" s="14"/>
+      <c r="D64" s="14"/>
     </row>
     <row r="65" ht="14.25" spans="1:4">
       <c r="A65" s="1" t="s">
@@ -4134,54 +4131,54 @@
       <c r="B65" s="1">
         <v>1</v>
       </c>
-      <c r="C65" s="16"/>
-      <c r="D65" s="16"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="14"/>
     </row>
     <row r="66" ht="14.25" spans="1:4">
-      <c r="A66" s="16" t="s">
+      <c r="A66" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B66" s="16">
+      <c r="B66" s="14">
         <v>2.2</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="16"/>
+      <c r="C66" s="14"/>
+      <c r="D66" s="14"/>
     </row>
     <row r="67" ht="14.25" spans="1:4">
-      <c r="A67" s="16" t="s">
+      <c r="A67" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B67" s="16">
+      <c r="B67" s="14">
         <v>4</v>
       </c>
-      <c r="C67" s="16"/>
-      <c r="D67" s="16"/>
+      <c r="C67" s="14"/>
+      <c r="D67" s="14"/>
     </row>
     <row r="68" ht="14.25" spans="1:5">
-      <c r="A68" s="16" t="s">
+      <c r="A68" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B68" s="16">
+      <c r="B68" s="14">
         <v>0.995</v>
       </c>
-      <c r="C68" s="16"/>
-      <c r="D68" s="16"/>
-      <c r="E68" s="24"/>
+      <c r="C68" s="14"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="23"/>
     </row>
     <row r="69" ht="14.25" spans="1:7">
-      <c r="A69" s="26" t="s">
+      <c r="A69" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="B69" s="26" t="s">
+      <c r="B69" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C69" s="26" t="s">
+      <c r="C69" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="D69" s="26" t="s">
+      <c r="D69" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="E69" s="27" t="s">
+      <c r="E69" s="26" t="s">
         <v>38</v>
       </c>
       <c r="F69" t="s">
@@ -4207,7 +4204,7 @@
         <f>FLOOR($B$65*POWER(A70,$B$66)*B70,1)</f>
         <v>3</v>
       </c>
-      <c r="E70" s="27"/>
+      <c r="E70" s="26"/>
       <c r="F70">
         <f>1+B70*((A70-1)*$B$63/100)</f>
         <v>1</v>
@@ -4233,7 +4230,7 @@
         <f t="shared" ref="D70:D104" si="7">FLOOR($B$65*POWER(A71,$B$66)*B71,1)</f>
         <v>18</v>
       </c>
-      <c r="E71" s="27"/>
+      <c r="E71" s="26"/>
       <c r="F71">
         <f t="shared" ref="F71:F102" si="8">1+B71*((A71-1)*$B$63/100)</f>
         <v>1.039601</v>
@@ -4259,7 +4256,7 @@
         <f t="shared" si="7"/>
         <v>44</v>
       </c>
-      <c r="E72" s="27"/>
+      <c r="E72" s="26"/>
       <c r="F72">
         <f t="shared" si="8"/>
         <v>1.07880599</v>
@@ -4285,7 +4282,7 @@
         <f t="shared" si="7"/>
         <v>82</v>
       </c>
-      <c r="E73" s="27"/>
+      <c r="E73" s="26"/>
       <c r="F73">
         <f t="shared" si="8"/>
         <v>1.117617940075</v>
@@ -4311,7 +4308,7 @@
         <f t="shared" si="7"/>
         <v>134</v>
       </c>
-      <c r="E74" s="27"/>
+      <c r="E74" s="26"/>
       <c r="F74">
         <f t="shared" si="8"/>
         <v>1.1560398004995</v>
@@ -4337,7 +4334,7 @@
         <f t="shared" si="7"/>
         <v>199</v>
       </c>
-      <c r="E75" s="27"/>
+      <c r="E75" s="26"/>
       <c r="F75">
         <f t="shared" si="8"/>
         <v>1.19407450187125</v>
@@ -4363,7 +4360,7 @@
         <f t="shared" si="7"/>
         <v>279</v>
       </c>
-      <c r="E76" s="27"/>
+      <c r="E76" s="26"/>
       <c r="F76">
         <f t="shared" si="8"/>
         <v>1.23172495523428</v>
@@ -4389,7 +4386,7 @@
         <f t="shared" si="7"/>
         <v>372</v>
       </c>
-      <c r="E77" s="27"/>
+      <c r="E77" s="26"/>
       <c r="F77">
         <f t="shared" si="8"/>
         <v>1.26899405220112</v>
@@ -4415,7 +4412,7 @@
         <f t="shared" si="7"/>
         <v>480</v>
       </c>
-      <c r="E78" s="27"/>
+      <c r="E78" s="26"/>
       <c r="F78">
         <f t="shared" si="8"/>
         <v>1.30588466507442</v>
@@ -4441,7 +4438,7 @@
         <f t="shared" si="7"/>
         <v>602</v>
       </c>
-      <c r="E79" s="27"/>
+      <c r="E79" s="26"/>
       <c r="F79">
         <f t="shared" si="8"/>
         <v>1.34239964696768</v>
@@ -4467,7 +4464,7 @@
         <f t="shared" si="7"/>
         <v>739</v>
       </c>
-      <c r="E80" s="27"/>
+      <c r="E80" s="26"/>
       <c r="F80">
         <f t="shared" si="8"/>
         <v>1.37854183192538</v>
@@ -4493,7 +4490,7 @@
         <f t="shared" si="7"/>
         <v>891</v>
       </c>
-      <c r="E81" s="27"/>
+      <c r="E81" s="26"/>
       <c r="F81">
         <f t="shared" si="8"/>
         <v>1.41431403504233</v>
@@ -4519,7 +4516,7 @@
         <f t="shared" si="7"/>
         <v>1057</v>
       </c>
-      <c r="E82" s="27"/>
+      <c r="E82" s="26"/>
       <c r="F82">
         <f t="shared" si="8"/>
         <v>1.44971905258231</v>
@@ -4545,7 +4542,7 @@
         <f t="shared" si="7"/>
         <v>1238</v>
       </c>
-      <c r="E83" s="27"/>
+      <c r="E83" s="26"/>
       <c r="F83">
         <f t="shared" si="8"/>
         <v>1.48475966209601</v>
@@ -4571,7 +4568,7 @@
         <f t="shared" si="7"/>
         <v>1434</v>
       </c>
-      <c r="E84" s="27"/>
+      <c r="E84" s="26"/>
       <c r="F84">
         <f t="shared" si="8"/>
         <v>1.51943862253826</v>
@@ -4597,7 +4594,7 @@
         <f t="shared" si="7"/>
         <v>1645</v>
       </c>
-      <c r="E85" s="27"/>
+      <c r="E85" s="26"/>
       <c r="F85">
         <f t="shared" si="8"/>
         <v>1.55375867438454</v>
@@ -4623,7 +4620,7 @@
         <f t="shared" si="7"/>
         <v>1870</v>
       </c>
-      <c r="E86" s="27"/>
+      <c r="E86" s="26"/>
       <c r="F86">
         <f t="shared" si="8"/>
         <v>1.58772253974679</v>
@@ -4649,7 +4646,7 @@
         <f t="shared" si="7"/>
         <v>2110</v>
       </c>
-      <c r="E87" s="27"/>
+      <c r="E87" s="26"/>
       <c r="F87">
         <f t="shared" si="8"/>
         <v>1.62133292248856</v>
@@ -4675,7 +4672,7 @@
         <f t="shared" si="7"/>
         <v>2365</v>
       </c>
-      <c r="E88" s="27"/>
+      <c r="E88" s="26"/>
       <c r="F88">
         <f t="shared" si="8"/>
         <v>1.65459250833942</v>
@@ -4701,7 +4698,7 @@
         <f t="shared" si="7"/>
         <v>2635</v>
       </c>
-      <c r="E89" s="27"/>
+      <c r="E89" s="26"/>
       <c r="F89">
         <f t="shared" si="8"/>
         <v>1.68750396500871</v>
@@ -4727,7 +4724,7 @@
         <f t="shared" si="7"/>
         <v>2918</v>
       </c>
-      <c r="E90" s="27"/>
+      <c r="E90" s="26"/>
       <c r="F90">
         <f t="shared" si="8"/>
         <v>1.7200699422986</v>
@@ -4753,7 +4750,7 @@
         <f t="shared" si="7"/>
         <v>3217</v>
       </c>
-      <c r="E91" s="27"/>
+      <c r="E91" s="26"/>
       <c r="F91">
         <f t="shared" si="8"/>
         <v>1.75229307221646</v>
@@ -4779,7 +4776,7 @@
         <f t="shared" si="7"/>
         <v>3530</v>
       </c>
-      <c r="E92" s="27"/>
+      <c r="E92" s="26"/>
       <c r="F92">
         <f t="shared" si="8"/>
         <v>1.78417596908658</v>
@@ -4805,7 +4802,7 @@
         <f t="shared" si="7"/>
         <v>3857</v>
       </c>
-      <c r="E93" s="27"/>
+      <c r="E93" s="26"/>
       <c r="F93">
         <f t="shared" si="8"/>
         <v>1.8157212296612</v>
@@ -4831,7 +4828,7 @@
         <f t="shared" si="7"/>
         <v>4198</v>
       </c>
-      <c r="E94" s="27"/>
+      <c r="E94" s="26"/>
       <c r="F94">
         <f t="shared" si="8"/>
         <v>1.84693143323085</v>
@@ -4857,7 +4854,7 @@
         <f t="shared" si="7"/>
         <v>4554</v>
       </c>
-      <c r="E95" s="27"/>
+      <c r="E95" s="26"/>
       <c r="F95">
         <f t="shared" si="8"/>
         <v>1.87780914173406</v>
@@ -4883,7 +4880,7 @@
         <f t="shared" si="7"/>
         <v>4923</v>
       </c>
-      <c r="E96" s="27"/>
+      <c r="E96" s="26"/>
       <c r="F96">
         <f t="shared" si="8"/>
         <v>1.9083568998664</v>
@@ -4909,7 +4906,7 @@
         <f t="shared" si="7"/>
         <v>5307</v>
       </c>
-      <c r="E97" s="27"/>
+      <c r="E97" s="26"/>
       <c r="F97">
         <f t="shared" si="8"/>
         <v>1.93857723518888</v>
@@ -4935,7 +4932,7 @@
         <f t="shared" si="7"/>
         <v>5704</v>
       </c>
-      <c r="E98" s="27"/>
+      <c r="E98" s="26"/>
       <c r="F98">
         <f t="shared" si="8"/>
         <v>1.96847265823564</v>
@@ -4961,7 +4958,7 @@
         <f t="shared" si="7"/>
         <v>6115</v>
       </c>
-      <c r="E99" s="27"/>
+      <c r="E99" s="26"/>
       <c r="F99">
         <f t="shared" si="8"/>
         <v>1.99804566262105</v>
@@ -4987,7 +4984,7 @@
         <f t="shared" si="7"/>
         <v>6539</v>
       </c>
-      <c r="E100" s="27"/>
+      <c r="E100" s="26"/>
       <c r="F100">
         <f t="shared" si="8"/>
         <v>2.02729872514615</v>
@@ -5013,7 +5010,7 @@
         <f t="shared" si="7"/>
         <v>6977</v>
       </c>
-      <c r="E101" s="27"/>
+      <c r="E101" s="26"/>
       <c r="F101">
         <f t="shared" si="8"/>
         <v>2.05623430590443</v>
@@ -5039,7 +5036,7 @@
         <f t="shared" si="7"/>
         <v>7429</v>
       </c>
-      <c r="E102" s="27"/>
+      <c r="E102" s="26"/>
       <c r="F102">
         <f t="shared" si="8"/>
         <v>2.084854848387</v>
@@ -5065,7 +5062,7 @@
         <f t="shared" si="7"/>
         <v>7894</v>
       </c>
-      <c r="E103" s="27"/>
+      <c r="E103" s="26"/>
       <c r="F103">
         <f t="shared" ref="F103:F119" si="11">1+B103*((A103-1)*$B$63/100)</f>
         <v>2.1131627795871</v>
@@ -5091,7 +5088,7 @@
         <f t="shared" si="7"/>
         <v>8371</v>
       </c>
-      <c r="E104" s="27"/>
+      <c r="E104" s="26"/>
       <c r="F104">
         <f t="shared" si="11"/>
         <v>2.14116051010399</v>
@@ -5117,7 +5114,7 @@
         <f t="shared" ref="D105:D119" si="14">FLOOR($B$65*POWER(A105,$B$66)*B105,1)</f>
         <v>8862</v>
       </c>
-      <c r="E105" s="27"/>
+      <c r="E105" s="26"/>
       <c r="F105">
         <f t="shared" si="11"/>
         <v>2.16885043424622</v>
@@ -5143,7 +5140,7 @@
         <f t="shared" si="14"/>
         <v>9366</v>
       </c>
-      <c r="E106" s="27"/>
+      <c r="E106" s="26"/>
       <c r="F106">
         <f t="shared" si="11"/>
         <v>2.19623493013427</v>
@@ -5169,7 +5166,7 @@
         <f t="shared" si="14"/>
         <v>9882</v>
       </c>
-      <c r="E107" s="27"/>
+      <c r="E107" s="26"/>
       <c r="F107">
         <f t="shared" si="11"/>
         <v>2.22331635980259</v>
@@ -5195,7 +5192,7 @@
         <f t="shared" si="14"/>
         <v>10411</v>
       </c>
-      <c r="E108" s="27"/>
+      <c r="E108" s="26"/>
       <c r="F108">
         <f t="shared" si="11"/>
         <v>2.25009706930097</v>
@@ -5221,7 +5218,7 @@
         <f t="shared" si="14"/>
         <v>10952</v>
       </c>
-      <c r="E109" s="27"/>
+      <c r="E109" s="26"/>
       <c r="F109">
         <f t="shared" si="11"/>
         <v>2.27657938879537</v>
@@ -5247,7 +5244,7 @@
         <f t="shared" si="14"/>
         <v>11506</v>
       </c>
-      <c r="E110" s="27"/>
+      <c r="E110" s="26"/>
       <c r="F110">
         <f t="shared" si="11"/>
         <v>2.3027656326681</v>
@@ -5273,7 +5270,7 @@
         <f t="shared" si="14"/>
         <v>12071</v>
       </c>
-      <c r="E111" s="27"/>
+      <c r="E111" s="26"/>
       <c r="F111">
         <f t="shared" si="11"/>
         <v>2.32865809961738</v>
@@ -5299,7 +5296,7 @@
         <f t="shared" si="14"/>
         <v>12649</v>
       </c>
-      <c r="E112" s="27"/>
+      <c r="E112" s="26"/>
       <c r="F112">
         <f t="shared" si="11"/>
         <v>2.35425907275634</v>
@@ -5325,7 +5322,7 @@
         <f t="shared" si="14"/>
         <v>13239</v>
       </c>
-      <c r="E113" s="27"/>
+      <c r="E113" s="26"/>
       <c r="F113">
         <f t="shared" si="11"/>
         <v>2.37957081971143</v>
@@ -5351,7 +5348,7 @@
         <f t="shared" si="14"/>
         <v>13840</v>
       </c>
-      <c r="E114" s="27"/>
+      <c r="E114" s="26"/>
       <c r="F114">
         <f t="shared" si="11"/>
         <v>2.40459559272015</v>
@@ -5377,7 +5374,7 @@
         <f t="shared" si="14"/>
         <v>14454</v>
       </c>
-      <c r="E115" s="27"/>
+      <c r="E115" s="26"/>
       <c r="F115">
         <f t="shared" si="11"/>
         <v>2.42933562872829</v>
@@ -5403,7 +5400,7 @@
         <f t="shared" si="14"/>
         <v>15078</v>
       </c>
-      <c r="E116" s="27"/>
+      <c r="E116" s="26"/>
       <c r="F116">
         <f t="shared" si="11"/>
         <v>2.45379314948653</v>
@@ -5429,7 +5426,7 @@
         <f t="shared" si="14"/>
         <v>15714</v>
       </c>
-      <c r="E117" s="27"/>
+      <c r="E117" s="26"/>
       <c r="F117">
         <f t="shared" si="11"/>
         <v>2.47797036164647</v>
@@ -5455,7 +5452,7 @@
         <f t="shared" si="14"/>
         <v>16361</v>
       </c>
-      <c r="E118" s="27"/>
+      <c r="E118" s="26"/>
       <c r="F118">
         <f t="shared" si="11"/>
         <v>2.50186945685607</v>
@@ -5481,7 +5478,7 @@
         <f t="shared" si="14"/>
         <v>17019</v>
       </c>
-      <c r="E119" s="27"/>
+      <c r="E119" s="26"/>
       <c r="F119">
         <f t="shared" si="11"/>
         <v>2.52549261185454</v>
@@ -5504,7 +5501,7 @@
       <c r="D121" s="1"/>
     </row>
     <row r="122" ht="28.5" spans="1:4">
-      <c r="A122" s="25" t="s">
+      <c r="A122" s="24" t="s">
         <v>41</v>
       </c>
       <c r="C122" s="1"/>
@@ -5939,10 +5936,10 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="22" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6118,10 +6115,10 @@
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="13">
+      <c r="A25" s="12">
         <v>20</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="12">
         <f t="shared" si="1"/>
         <v>960</v>
       </c>
@@ -6323,20 +6320,20 @@
   </cols>
   <sheetData>
     <row r="12" ht="219" customHeight="1" spans="1:1">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="6" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="8"/>
+      <c r="A16" s="6"/>
     </row>
     <row r="17" ht="299.25" spans="1:1">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="6" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="8"/>
+      <c r="A21" s="6"/>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
@@ -6344,10 +6341,10 @@
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="8"/>
+      <c r="A24" s="6"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="8"/>
+      <c r="A26" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6371,46 +6368,46 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="18" customFormat="1" ht="27" spans="1:7">
-      <c r="A1" s="19" t="s">
+    <row r="1" s="17" customFormat="1" ht="27" spans="1:7">
+      <c r="A1" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="17" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="2" ht="273" customHeight="1" spans="1:7">
-      <c r="A2" s="20">
+      <c r="A2" s="19">
         <v>10000</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="6" t="s">
         <v>61</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -6418,52 +6415,52 @@
       </c>
     </row>
     <row r="3" ht="102" customHeight="1" spans="1:7">
-      <c r="A3" s="20"/>
-      <c r="B3" s="20" t="s">
+      <c r="A3" s="19"/>
+      <c r="B3" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="20"/>
+      <c r="E3" s="19"/>
       <c r="G3" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="4" ht="119" customHeight="1" spans="1:5">
-      <c r="A4" s="20"/>
-      <c r="B4" s="20" t="s">
+      <c r="A4" s="19"/>
+      <c r="B4" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="E4" s="20"/>
+      <c r="E4" s="19"/>
     </row>
     <row r="5" ht="118" customHeight="1" spans="1:5">
-      <c r="A5" s="20"/>
-      <c r="B5" s="20" t="s">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="20"/>
+      <c r="E5" s="19"/>
     </row>
     <row r="6" ht="28.5" spans="2:3">
       <c r="B6" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="6" t="s">
         <v>74</v>
       </c>
     </row>
@@ -6493,7 +6490,7 @@
         <v>75</v>
       </c>
       <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="D6" s="6"/>
     </row>
     <row r="7" spans="5:5">
       <c r="E7" s="1" t="s">
@@ -6501,10 +6498,10 @@
       </c>
     </row>
     <row r="9" ht="16.5" spans="2:5">
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="9">
         <v>100</v>
       </c>
       <c r="D9" s="5" t="s">
@@ -6515,8 +6512,8 @@
       </c>
     </row>
     <row r="10" ht="16.5" spans="2:5">
-      <c r="B10" s="9"/>
-      <c r="C10" s="10">
+      <c r="B10" s="8"/>
+      <c r="C10" s="9">
         <v>101</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -6527,8 +6524,8 @@
       </c>
     </row>
     <row r="11" ht="16.5" spans="2:5">
-      <c r="B11" s="9"/>
-      <c r="C11" s="10">
+      <c r="B11" s="8"/>
+      <c r="C11" s="9">
         <v>102</v>
       </c>
       <c r="D11" s="5" t="s">
@@ -6578,13 +6575,13 @@
       <c r="D15" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="10" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="2:5">
-      <c r="B16" s="9"/>
-      <c r="C16" s="10">
+      <c r="B16" s="8"/>
+      <c r="C16" s="9">
         <v>107</v>
       </c>
       <c r="D16" s="5" t="s">
@@ -6595,8 +6592,8 @@
       </c>
     </row>
     <row r="17" ht="16.5" spans="2:5">
-      <c r="B17" s="9"/>
-      <c r="C17" s="10">
+      <c r="B17" s="8"/>
+      <c r="C17" s="9">
         <v>108</v>
       </c>
       <c r="D17" s="5" t="s">
@@ -6607,8 +6604,8 @@
       </c>
     </row>
     <row r="18" ht="16.5" spans="2:5">
-      <c r="B18" s="9"/>
-      <c r="C18" s="10">
+      <c r="B18" s="8"/>
+      <c r="C18" s="9">
         <v>109</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -6619,16 +6616,16 @@
       </c>
     </row>
     <row r="19" ht="16.5" spans="2:3">
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
     </row>
     <row r="20" ht="16.5" spans="2:3">
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
     </row>
     <row r="21" ht="16.5" spans="2:5">
-      <c r="B21" s="9"/>
-      <c r="C21" s="10">
+      <c r="B21" s="8"/>
+      <c r="C21" s="9">
         <v>150</v>
       </c>
       <c r="D21" s="5" t="s">
@@ -6639,30 +6636,30 @@
       </c>
     </row>
     <row r="22" ht="16.5" spans="2:3">
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
     </row>
     <row r="23" ht="16.5" spans="2:3">
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
     </row>
     <row r="24" ht="16.5" spans="2:3">
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
     </row>
     <row r="25" ht="16.5" spans="2:3">
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
     </row>
     <row r="26" ht="16.5" spans="2:3">
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
     </row>
     <row r="27" ht="49.5" spans="2:5">
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="9">
         <v>200</v>
       </c>
       <c r="D27" s="5" t="s">
@@ -6671,8 +6668,8 @@
       <c r="E27" s="5"/>
     </row>
     <row r="28" ht="16.5" spans="2:5">
-      <c r="B28" s="9"/>
-      <c r="C28" s="10">
+      <c r="B28" s="8"/>
+      <c r="C28" s="9">
         <v>201</v>
       </c>
       <c r="D28" s="5" t="s">
@@ -6689,7 +6686,7 @@
       <c r="D29" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="10" t="s">
         <v>105</v>
       </c>
     </row>
@@ -6705,13 +6702,13 @@
       </c>
     </row>
     <row r="31" ht="28.5" spans="3:5">
-      <c r="C31" s="13">
+      <c r="C31" s="5">
         <v>204</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="10" t="s">
         <v>109</v>
       </c>
     </row>
@@ -6727,32 +6724,32 @@
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" spans="3:5">
-      <c r="C33" s="13">
+      <c r="C33" s="12">
         <v>206</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="E33" s="13" t="s">
+      <c r="E33" s="12" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="34" ht="45" customHeight="1" spans="3:5">
-      <c r="C34" s="13">
+      <c r="C34" s="12">
         <v>207</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E34" s="13" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="35" spans="3:5">
-      <c r="C35" s="13">
+      <c r="C35" s="12">
         <v>208</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="12" t="s">
         <v>116</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -6760,10 +6757,10 @@
       </c>
     </row>
     <row r="36" spans="3:5">
-      <c r="C36" s="13">
+      <c r="C36" s="12">
         <v>209</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="12" t="s">
         <v>118</v>
       </c>
       <c r="E36" s="1" t="s">
@@ -6771,107 +6768,107 @@
       </c>
     </row>
     <row r="37" ht="16.5" spans="2:5">
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="E37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="E37" s="6"/>
     </row>
     <row r="38" ht="16.5" spans="2:5">
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="E38" s="8"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="E38" s="6"/>
     </row>
     <row r="39" ht="16.5" spans="2:5">
-      <c r="B39" s="9"/>
-      <c r="C39" s="10">
+      <c r="B39" s="8"/>
+      <c r="C39" s="9">
         <v>250</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="E39" s="11" t="s">
+      <c r="E39" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="2:5">
-      <c r="B40" s="9"/>
-      <c r="C40" s="10">
+      <c r="B40" s="8"/>
+      <c r="C40" s="9">
         <v>251</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E40" s="10" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="2:5">
-      <c r="B41" s="9"/>
-      <c r="C41" s="10">
+      <c r="B41" s="8"/>
+      <c r="C41" s="9">
         <v>252</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E41" s="10" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="2:5">
-      <c r="B42" s="9"/>
-      <c r="C42" s="10">
+      <c r="B42" s="8"/>
+      <c r="C42" s="9">
         <v>255</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="E42" s="11"/>
+      <c r="E42" s="10"/>
     </row>
     <row r="43" ht="16.5" spans="2:5">
-      <c r="B43" s="9"/>
-      <c r="C43" s="10">
+      <c r="B43" s="8"/>
+      <c r="C43" s="9">
         <v>256</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="E43" s="11"/>
+      <c r="E43" s="10"/>
     </row>
     <row r="44" ht="16.5" spans="2:5">
-      <c r="B44" s="9"/>
-      <c r="C44" s="10">
+      <c r="B44" s="8"/>
+      <c r="C44" s="9">
         <v>257</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="E44" s="11"/>
+      <c r="E44" s="10"/>
     </row>
     <row r="45" ht="16.5" spans="2:5">
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="E45" s="8"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="E45" s="6"/>
     </row>
     <row r="46" ht="16.5" spans="2:5">
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="E46" s="8"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="E46" s="6"/>
     </row>
     <row r="47" ht="16.5" spans="2:5">
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="E47" s="8"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="E47" s="6"/>
     </row>
     <row r="48" ht="49.5" spans="2:5">
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="C48" s="9">
+      <c r="C48" s="8">
         <v>300</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E48" s="6" t="s">
         <v>130</v>
       </c>
     </row>
@@ -6882,7 +6879,7 @@
       <c r="D49" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="E49" s="6" t="s">
         <v>132</v>
       </c>
     </row>
@@ -6893,7 +6890,7 @@
       <c r="D50" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" s="6" t="s">
         <v>134</v>
       </c>
     </row>
@@ -6975,16 +6972,16 @@
       </c>
     </row>
     <row r="59" ht="49.5" spans="2:5">
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C59" s="9">
+      <c r="C59" s="8">
         <v>400</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E59" s="8" t="s">
+      <c r="E59" s="6" t="s">
         <v>151</v>
       </c>
     </row>
@@ -7003,8 +7000,8 @@
       <c r="C61" s="1">
         <v>402</v>
       </c>
-      <c r="D61" s="16"/>
-      <c r="E61" s="14"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="15"/>
     </row>
     <row r="62" spans="3:5">
       <c r="C62" s="1">
@@ -7013,7 +7010,7 @@
       <c r="D62" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="E62" s="11" t="s">
+      <c r="E62" s="10" t="s">
         <v>155</v>
       </c>
     </row>
@@ -7024,7 +7021,7 @@
       <c r="D63" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="E63" s="11" t="s">
+      <c r="E63" s="10" t="s">
         <v>157</v>
       </c>
     </row>
@@ -7035,7 +7032,7 @@
       <c r="D64" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E64" s="8" t="s">
+      <c r="E64" s="6" t="s">
         <v>159</v>
       </c>
     </row>
@@ -7046,65 +7043,65 @@
       <c r="D65" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E65" s="8" t="s">
+      <c r="E65" s="6" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="66" ht="16.5" spans="2:5">
-      <c r="B66" s="9"/>
+      <c r="B66" s="8"/>
       <c r="C66" s="1">
         <v>407</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E66" s="8" t="s">
+      <c r="E66" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="67" ht="16.5" spans="2:5">
-      <c r="B67" s="9"/>
+      <c r="B67" s="8"/>
       <c r="C67" s="1">
         <v>408</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E67" s="8" t="s">
+      <c r="E67" s="6" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="2:5">
-      <c r="B68" s="9"/>
+      <c r="B68" s="8"/>
       <c r="C68" s="1">
         <v>409</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E68" s="8" t="s">
+      <c r="E68" s="6" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="69" ht="16.5" spans="2:5">
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="E69" s="8"/>
+      <c r="B69" s="8"/>
+      <c r="C69" s="8"/>
+      <c r="E69" s="6"/>
     </row>
     <row r="70" ht="16.5" spans="2:5">
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="E70" s="8"/>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
+      <c r="E70" s="6"/>
     </row>
     <row r="71" ht="28.5" spans="2:5">
-      <c r="B71" s="9" t="s">
+      <c r="B71" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C71" s="9"/>
+      <c r="C71" s="8"/>
       <c r="D71" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E71" s="8" t="s">
+      <c r="E71" s="6" t="s">
         <v>170</v>
       </c>
     </row>
@@ -7130,70 +7127,70 @@
       </c>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="17" t="s">
+      <c r="A77" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="B77" s="17" t="s">
+      <c r="B77" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="C77" s="17"/>
-      <c r="D77" s="17" t="s">
+      <c r="C77" s="16"/>
+      <c r="D77" s="16" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="17" t="s">
+      <c r="A78" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="B78" s="17" t="s">
+      <c r="B78" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="C78" s="17"/>
-      <c r="D78" s="17" t="s">
+      <c r="C78" s="16"/>
+      <c r="D78" s="16" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="17" t="s">
+      <c r="A79" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="B79" s="17" t="s">
+      <c r="B79" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="C79" s="17"/>
-      <c r="D79" s="17" t="s">
+      <c r="C79" s="16"/>
+      <c r="D79" s="16" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="80" spans="4:4">
-      <c r="D80" s="8"/>
+      <c r="D80" s="6"/>
     </row>
     <row r="81" spans="4:4">
-      <c r="D81" s="8"/>
+      <c r="D81" s="6"/>
     </row>
     <row r="82" spans="4:4">
-      <c r="D82" s="8"/>
+      <c r="D82" s="6"/>
     </row>
     <row r="83" spans="4:4">
-      <c r="D83" s="8"/>
+      <c r="D83" s="6"/>
     </row>
     <row r="84" spans="4:4">
-      <c r="D84" s="8"/>
+      <c r="D84" s="6"/>
     </row>
     <row r="85" spans="4:4">
-      <c r="D85" s="8"/>
+      <c r="D85" s="6"/>
     </row>
     <row r="86" spans="4:4">
-      <c r="D86" s="8"/>
+      <c r="D86" s="6"/>
     </row>
     <row r="87" spans="4:4">
-      <c r="D87" s="8"/>
+      <c r="D87" s="6"/>
     </row>
     <row r="88" ht="28.5" spans="2:4">
       <c r="B88" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="D88" s="8" t="s">
+      <c r="D88" s="6" t="s">
         <v>183</v>
       </c>
     </row>
